--- a/testdata/NorthStar_Logistics_Jan2026.xlsx
+++ b/testdata/NorthStar_Logistics_Jan2026.xlsx
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>85125</v>
+        <v>374850</v>
       </c>
     </row>
     <row r="6">
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>833175</v>
+        <v>651450</v>
       </c>
     </row>
     <row r="23">
